--- a/2_profile_generator/control_file_profile_generator.xlsx
+++ b/2_profile_generator/control_file_profile_generator.xlsx
@@ -1,23 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vub-my.sharepoint.com/personal/sebastian_sterl_vub_be/Documents/Documenten/VUB Work Files/MSR code repo/2_profile_generator/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_DDEDB4A8BED604FDB0E8A2ADE1532E5F302D5BA1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FE0AEFD-B7F4-4455-9CF1-36869681E201}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="paths"/>
-    <sheet r:id="rId2" sheetId="2" name="configurations"/>
-    <sheet r:id="rId3" sheetId="3" name="parameters"/>
-    <sheet r:id="rId4" sheetId="4" name="datasets"/>
+    <sheet name="paths" sheetId="1" r:id="rId1"/>
+    <sheet name="configurations" sheetId="2" r:id="rId2"/>
+    <sheet name="parameters" sheetId="3" r:id="rId3"/>
+    <sheet name="datasets" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="55">
   <si>
     <t>datasets</t>
   </si>
@@ -258,18 +264,6 @@
     <t>paths</t>
   </si>
   <si>
-    <t>output_folder_msr_creator</t>
-  </si>
-  <si>
-    <t>C:\Dev\model_supply_regions\Model-Supply-Regions-MSR-Toolset\outputs\1_msr_creator</t>
-  </si>
-  <si>
-    <t>Folder path where msr creator ouputs are located.</t>
-  </si>
-  <si>
-    <t>input_datasets_folder</t>
-  </si>
-  <si>
     <t>C:\Users\mastt\OneDrive - VITO\Documents\21_WP1\RawData\model_supply_regions\workflow\inputs\2022 MSR Toolset Inputs</t>
   </si>
   <si>
@@ -279,21 +273,20 @@
     <t>output_folder</t>
   </si>
   <si>
-    <t>C:\Dev\model_supply_regions\Model-Supply-Regions-MSR-Toolset\outputs\2_profile_generator</t>
-  </si>
-  <si>
-    <t>output_folder_profile_generator</t>
-  </si>
-  <si>
-    <t>Folder path where profile generator ouputs are located.</t>
+    <t>input_folder_datasets</t>
+  </si>
+  <si>
+    <t>Folder path where outputs are located.</t>
+  </si>
+  <si>
+    <t>C:\Dev\model_supply_regions\Model-Supply-Regions-MSR-Toolset\outputs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,6 +312,21 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -348,115 +356,106 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C13" displayName="Table4" name="Table4" id="1" totalsRowShown="0">
-  <autoFilter ref="A1:C13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2" displayName="Table2" ref="A1:C3" totalsRowShown="0">
+  <autoFilter ref="A1:C3" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="3">
-    <tableColumn name="datasets" id="1"/>
-    <tableColumn name="value" id="2"/>
-    <tableColumn name="comments" id="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="paths"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="value"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="comments"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C4" displayName="Table5" name="Table5" id="2" totalsRowShown="0">
-  <autoFilter ref="A1:C4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table1" displayName="Table1" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn name="parameters" id="1"/>
-    <tableColumn name="value" id="2"/>
-    <tableColumn name="comments" id="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="configurations"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="value"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="comments"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C5" displayName="Table1" name="Table1" id="3" totalsRowShown="0">
-  <autoFilter ref="A1:C5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table5" displayName="Table5" ref="A1:C4" totalsRowShown="0">
+  <autoFilter ref="A1:C4" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn name="configurations" id="1"/>
-    <tableColumn name="value" id="2"/>
-    <tableColumn name="comments" id="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="parameters"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="value"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="comments"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C5" displayName="Table2" name="Table2" id="4" totalsRowShown="0">
-  <autoFilter ref="A1:C5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table4" displayName="Table4" ref="A1:C13" totalsRowShown="0">
+  <autoFilter ref="A1:C13" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn name="paths" id="1"/>
-    <tableColumn name="value" id="2"/>
-    <tableColumn name="comments" id="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="datasets"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="value"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="comments"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -465,10 +464,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -506,71 +505,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -598,7 +597,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -621,11 +620,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -634,13 +633,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -650,7 +649,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -659,7 +658,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -668,7 +667,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -676,10 +675,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -744,19 +743,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="5" width="36.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="58.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="52.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="36.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.81640625" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -767,46 +766,26 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="16"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -818,67 +797,67 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="6" width="48.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="12" width="20.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="60.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="48.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.7265625" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="8">
         <v>0</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5" customFormat="1" s="3">
+    <row r="3" spans="1:3" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="12">
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5" customFormat="1" s="3">
+    <row r="4" spans="1:3" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="12">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5" customFormat="1" s="3">
+    <row r="5" spans="1:3" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="12">
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -894,55 +873,53 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="11" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="11" width="11.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="8">
         <v>8784</v>
       </c>
-      <c r="C2" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="7" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <v>3000</v>
       </c>
-      <c r="C3" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="7" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>100</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" t="s">
         <v>41</v>
       </c>
     </row>
@@ -955,19 +932,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="5" width="36.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="36.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="36.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="2" width="36.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.7265625" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -978,7 +954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row r="2" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -989,7 +965,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row r="3" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1000,7 +976,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row r="4" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -1011,7 +987,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
@@ -1022,7 +998,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row r="6" spans="1:3" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
@@ -1033,7 +1009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row r="7" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
@@ -1044,7 +1020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>21</v>
       </c>
@@ -1055,7 +1031,7 @@
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row r="9" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
@@ -1066,7 +1042,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row r="10" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>27</v>
       </c>
@@ -1077,7 +1053,7 @@
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>30</v>
       </c>
@@ -1086,7 +1062,7 @@
       </c>
       <c r="C11" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row r="12" spans="1:3" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>32</v>
       </c>
@@ -1097,7 +1073,7 @@
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>35</v>
       </c>

--- a/2_profile_generator/control_file_profile_generator.xlsx
+++ b/2_profile_generator/control_file_profile_generator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vub-my.sharepoint.com/personal/sebastian_sterl_vub_be/Documents/Documenten/VUB Work Files/MSR code repo/2_profile_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_DDEDB4A8BED604FDB0E8A2ADE1532E5F302D5BA1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FE0AEFD-B7F4-4455-9CF1-36869681E201}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_DDEDB4A8BED604FDB0E8A2ADE1532E5F302D5BA1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8C93EF0-7DF2-4221-8009-1AE5A8E875C2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="paths" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
   <si>
     <t>datasets</t>
   </si>
@@ -104,6 +104,123 @@
     <t>2m_instant.nc</t>
   </si>
   <si>
+    <t>geopotential</t>
+  </si>
+  <si>
+    <t>z_instant.nc</t>
+  </si>
+  <si>
+    <t>direct_solar_radiation_at_surface</t>
+  </si>
+  <si>
+    <t>dsr_acc.nc</t>
+  </si>
+  <si>
+    <t>albedo_for_diffuse_radiation</t>
+  </si>
+  <si>
+    <t>albedo_acc.nc</t>
+  </si>
+  <si>
+    <t>surface_solar_radiation_downwards</t>
+  </si>
+  <si>
+    <t>ssrd_acc.nc</t>
+  </si>
+  <si>
+    <t>path to accumulated ERA 5 data (ssrd)</t>
+  </si>
+  <si>
+    <t>three_iec_turbine_power_curves</t>
+  </si>
+  <si>
+    <t>Wind speed IEC Classes</t>
+  </si>
+  <si>
+    <t>Wind turbine power curves for three IEC classes</t>
+  </si>
+  <si>
+    <t>file_name_wind_resource_raster</t>
+  </si>
+  <si>
+    <t>ECU_wind-speed_100m</t>
+  </si>
+  <si>
+    <t>file_name_solarpv_resource_raster</t>
+  </si>
+  <si>
+    <t>solarpv_GHI_2026</t>
+  </si>
+  <si>
+    <t>file_name_regions</t>
+  </si>
+  <si>
+    <t>region_names</t>
+  </si>
+  <si>
+    <t>File name of csv file carrying list of regions for which MSR hourly profiles will be created.</t>
+  </si>
+  <si>
+    <t>file_name_region_utc_offset</t>
+  </si>
+  <si>
+    <t>region_utc_offsets</t>
+  </si>
+  <si>
+    <t>parameters</t>
+  </si>
+  <si>
+    <t>hours_in_year</t>
+  </si>
+  <si>
+    <t>elevation_threshold</t>
+  </si>
+  <si>
+    <t>wind_hub_height</t>
+  </si>
+  <si>
+    <t>Units: meters</t>
+  </si>
+  <si>
+    <t>configurations</t>
+  </si>
+  <si>
+    <t>run_code_for_solar_pv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Options=[0-No, 1-Yes]. </t>
+  </si>
+  <si>
+    <t>run_code_for_solar_csp</t>
+  </si>
+  <si>
+    <t>run_code_for_wind</t>
+  </si>
+  <si>
+    <t>run_code_for_offshore_wind</t>
+  </si>
+  <si>
+    <t>paths</t>
+  </si>
+  <si>
+    <t>C:\Users\mastt\OneDrive - VITO\Documents\21_WP1\RawData\model_supply_regions\workflow\inputs\2022 MSR Toolset Inputs</t>
+  </si>
+  <si>
+    <t>Folder path where input datasets are located.</t>
+  </si>
+  <si>
+    <t>output_folder</t>
+  </si>
+  <si>
+    <t>input_folder_datasets</t>
+  </si>
+  <si>
+    <t>Folder path where outputs are located.</t>
+  </si>
+  <si>
+    <t>C:\Dev\model_supply_regions\Model-Supply-Regions-MSR-Toolset\outputs</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">path to </t>
     </r>
@@ -126,14 +243,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>ERA 5 data (u10, v10, u100, v100, t2m, z)</t>
+      <t>ERA 5 data (t2m)</t>
     </r>
-  </si>
-  <si>
-    <t>geopotential</t>
-  </si>
-  <si>
-    <t>z_instant.nc</t>
   </si>
   <si>
     <r>
@@ -158,128 +269,23 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>ERA 5 data ( z)</t>
+      <t>ERA 5 data (z)</t>
     </r>
   </si>
   <si>
-    <t>direct_solar_radiation_at_surface</t>
-  </si>
-  <si>
-    <t>dsr_acc.nc</t>
-  </si>
-  <si>
-    <t>clear_sky_direct_solar_radiation_at_surface', 'total_sky_direct_solar_radiation_at_surface'</t>
-  </si>
-  <si>
-    <t>albedo_for_diffuse_radiation</t>
-  </si>
-  <si>
-    <t>albedo_acc.nc</t>
-  </si>
-  <si>
-    <t>near_ir_albedo_for_diffuse_radiation', 'uv_visible_albedo_for_diffuse_radiation'</t>
-  </si>
-  <si>
-    <t>surface_solar_radiation_downwards</t>
-  </si>
-  <si>
-    <t>ssrd_acc.nc</t>
-  </si>
-  <si>
-    <t>path to accumulated ERA 5 data (ssrd)</t>
-  </si>
-  <si>
-    <t>three_iec_turbine_power_curves</t>
-  </si>
-  <si>
-    <t>Wind speed IEC Classes</t>
-  </si>
-  <si>
-    <t>Wind turbine power curves for three IEC classes</t>
-  </si>
-  <si>
-    <t>file_name_wind_resource_raster</t>
-  </si>
-  <si>
-    <t>ECU_wind-speed_100m</t>
-  </si>
-  <si>
-    <t>Resource raster naming convention in MSR_Creator Outputs</t>
-  </si>
-  <si>
-    <t>file_name_solarpv_resource_raster</t>
-  </si>
-  <si>
-    <t>solarpv_GHI_2026</t>
-  </si>
-  <si>
-    <t>file_name_regions</t>
-  </si>
-  <si>
-    <t>region_names</t>
-  </si>
-  <si>
-    <t>File name of csv file carrying list of regions for which MSR hourly profiles will be created.</t>
-  </si>
-  <si>
-    <t>file_name_region_utc_offset</t>
-  </si>
-  <si>
-    <t>region_utc_offsets</t>
-  </si>
-  <si>
-    <t>parameters</t>
-  </si>
-  <si>
-    <t>hours_in_year</t>
-  </si>
-  <si>
-    <t>elevation_threshold</t>
-  </si>
-  <si>
-    <t>wind_hub_height</t>
-  </si>
-  <si>
-    <t>Units: meters</t>
-  </si>
-  <si>
-    <t>configurations</t>
-  </si>
-  <si>
-    <t>run_code_for_solar_pv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Options=[0-No, 1-Yes]. </t>
-  </si>
-  <si>
-    <t>run_code_for_solar_csp</t>
-  </si>
-  <si>
-    <t>run_code_for_wind</t>
-  </si>
-  <si>
-    <t>run_code_for_offshore_wind</t>
-  </si>
-  <si>
-    <t>paths</t>
-  </si>
-  <si>
-    <t>C:\Users\mastt\OneDrive - VITO\Documents\21_WP1\RawData\model_supply_regions\workflow\inputs\2022 MSR Toolset Inputs</t>
-  </si>
-  <si>
-    <t>Folder path where input datasets are located.</t>
-  </si>
-  <si>
-    <t>output_folder</t>
-  </si>
-  <si>
-    <t>input_folder_datasets</t>
-  </si>
-  <si>
-    <t>Folder path where outputs are located.</t>
-  </si>
-  <si>
-    <t>C:\Dev\model_supply_regions\Model-Supply-Regions-MSR-Toolset\outputs</t>
+    <t>path to accumulated ERA 5 data (clear_sky_direct_solar_radiation_at_surface', 'total_sky_direct_solar_radiation_at_surface')</t>
+  </si>
+  <si>
+    <t>path to accumulated ERA 5 data (near_ir_albedo_for_diffuse_radiation', 'uv_visible_albedo_for_diffuse_radiation')</t>
+  </si>
+  <si>
+    <t>File name with average wind speed map</t>
+  </si>
+  <si>
+    <t>File name with average solar GHI map</t>
+  </si>
+  <si>
+    <t>File name of csv file with offsets per region of time zone compared to UTC</t>
   </si>
 </sst>
 </file>
@@ -329,15 +335,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -352,11 +364,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -393,12 +414,41 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -453,7 +503,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="datasets"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="value"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="comments"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -750,14 +800,14 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.36328125" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="58.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.26953125" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -768,24 +818,24 @@
     </row>
     <row r="2" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -804,14 +854,14 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.81640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="60.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.54296875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>1</v>
@@ -822,46 +872,46 @@
     </row>
     <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B2" s="8">
         <v>0</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B3" s="12">
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B4" s="12">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B5" s="12">
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -880,14 +930,14 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.54296875" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>1</v>
@@ -898,7 +948,7 @@
     </row>
     <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B2" s="8">
         <v>8784</v>
@@ -906,7 +956,7 @@
     </row>
     <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B3" s="9">
         <v>3000</v>
@@ -914,13 +964,13 @@
     </row>
     <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B4" s="8">
         <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -940,7 +990,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="36.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.26953125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -954,133 +1004,137 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>11</v>
+      <c r="C4" s="13" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="C6" s="13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>20</v>
+      <c r="C7" s="14" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="4" t="s">
+    </row>
+    <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>29</v>
+      <c r="C10" s="13" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" spans="1:3" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="15" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2_profile_generator/control_file_profile_generator.xlsx
+++ b/2_profile_generator/control_file_profile_generator.xlsx
@@ -1,24 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vub-my.sharepoint.com/personal/sebastian_sterl_vub_be/Documents/Documenten/VUB Work Files/MSR code repo/2_profile_generator/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_DDEDB4A8BED604FDB0E8A2ADE1532E5F302D5BA1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8C93EF0-7DF2-4221-8009-1AE5A8E875C2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="paths" sheetId="1" r:id="rId1"/>
-    <sheet name="configurations" sheetId="2" r:id="rId2"/>
-    <sheet name="parameters" sheetId="3" r:id="rId3"/>
-    <sheet name="datasets" sheetId="4" r:id="rId4"/>
+    <sheet r:id="rId1" sheetId="1" name="paths"/>
+    <sheet r:id="rId2" sheetId="2" name="configurations"/>
+    <sheet r:id="rId3" sheetId="3" name="parameters"/>
+    <sheet r:id="rId4" sheetId="4" name="datasets"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -37,7 +31,7 @@
     <t>10m_component_of_wind</t>
   </si>
   <si>
-    <t>10m_instant.nc</t>
+    <t>10m</t>
   </si>
   <si>
     <r>
@@ -69,7 +63,7 @@
     <t>100m_component_of_wind</t>
   </si>
   <si>
-    <t>100m_instant.nc</t>
+    <t>100m</t>
   </si>
   <si>
     <r>
@@ -101,124 +95,7 @@
     <t>2m_temperature</t>
   </si>
   <si>
-    <t>2m_instant.nc</t>
-  </si>
-  <si>
-    <t>geopotential</t>
-  </si>
-  <si>
-    <t>z_instant.nc</t>
-  </si>
-  <si>
-    <t>direct_solar_radiation_at_surface</t>
-  </si>
-  <si>
-    <t>dsr_acc.nc</t>
-  </si>
-  <si>
-    <t>albedo_for_diffuse_radiation</t>
-  </si>
-  <si>
-    <t>albedo_acc.nc</t>
-  </si>
-  <si>
-    <t>surface_solar_radiation_downwards</t>
-  </si>
-  <si>
-    <t>ssrd_acc.nc</t>
-  </si>
-  <si>
-    <t>path to accumulated ERA 5 data (ssrd)</t>
-  </si>
-  <si>
-    <t>three_iec_turbine_power_curves</t>
-  </si>
-  <si>
-    <t>Wind speed IEC Classes</t>
-  </si>
-  <si>
-    <t>Wind turbine power curves for three IEC classes</t>
-  </si>
-  <si>
-    <t>file_name_wind_resource_raster</t>
-  </si>
-  <si>
-    <t>ECU_wind-speed_100m</t>
-  </si>
-  <si>
-    <t>file_name_solarpv_resource_raster</t>
-  </si>
-  <si>
-    <t>solarpv_GHI_2026</t>
-  </si>
-  <si>
-    <t>file_name_regions</t>
-  </si>
-  <si>
-    <t>region_names</t>
-  </si>
-  <si>
-    <t>File name of csv file carrying list of regions for which MSR hourly profiles will be created.</t>
-  </si>
-  <si>
-    <t>file_name_region_utc_offset</t>
-  </si>
-  <si>
-    <t>region_utc_offsets</t>
-  </si>
-  <si>
-    <t>parameters</t>
-  </si>
-  <si>
-    <t>hours_in_year</t>
-  </si>
-  <si>
-    <t>elevation_threshold</t>
-  </si>
-  <si>
-    <t>wind_hub_height</t>
-  </si>
-  <si>
-    <t>Units: meters</t>
-  </si>
-  <si>
-    <t>configurations</t>
-  </si>
-  <si>
-    <t>run_code_for_solar_pv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Options=[0-No, 1-Yes]. </t>
-  </si>
-  <si>
-    <t>run_code_for_solar_csp</t>
-  </si>
-  <si>
-    <t>run_code_for_wind</t>
-  </si>
-  <si>
-    <t>run_code_for_offshore_wind</t>
-  </si>
-  <si>
-    <t>paths</t>
-  </si>
-  <si>
-    <t>C:\Users\mastt\OneDrive - VITO\Documents\21_WP1\RawData\model_supply_regions\workflow\inputs\2022 MSR Toolset Inputs</t>
-  </si>
-  <si>
-    <t>Folder path where input datasets are located.</t>
-  </si>
-  <si>
-    <t>output_folder</t>
-  </si>
-  <si>
-    <t>input_folder_datasets</t>
-  </si>
-  <si>
-    <t>Folder path where outputs are located.</t>
-  </si>
-  <si>
-    <t>C:\Dev\model_supply_regions\Model-Supply-Regions-MSR-Toolset\outputs</t>
+    <t>t2m</t>
   </si>
   <si>
     <r>
@@ -243,8 +120,14 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>ERA 5 data (t2m)</t>
-    </r>
+      <t>ERA 5 data (u10, v10, u100, v100, t2m, z)</t>
+    </r>
+  </si>
+  <si>
+    <t>geopotential</t>
+  </si>
+  <si>
+    <t>z</t>
   </si>
   <si>
     <r>
@@ -269,30 +152,142 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>ERA 5 data (z)</t>
-    </r>
-  </si>
-  <si>
-    <t>path to accumulated ERA 5 data (clear_sky_direct_solar_radiation_at_surface', 'total_sky_direct_solar_radiation_at_surface')</t>
-  </si>
-  <si>
-    <t>path to accumulated ERA 5 data (near_ir_albedo_for_diffuse_radiation', 'uv_visible_albedo_for_diffuse_radiation')</t>
-  </si>
-  <si>
-    <t>File name with average wind speed map</t>
-  </si>
-  <si>
-    <t>File name with average solar GHI map</t>
-  </si>
-  <si>
-    <t>File name of csv file with offsets per region of time zone compared to UTC</t>
+      <t>ERA 5 data ( z)</t>
+    </r>
+  </si>
+  <si>
+    <t>direct_solar_radiation_at_surface</t>
+  </si>
+  <si>
+    <t>dsr_acc.nc</t>
+  </si>
+  <si>
+    <t>clear_sky_direct_solar_radiation_at_surface', 'total_sky_direct_solar_radiation_at_surface'</t>
+  </si>
+  <si>
+    <t>albedo_for_diffuse_radiation</t>
+  </si>
+  <si>
+    <t>albedo_acc.nc</t>
+  </si>
+  <si>
+    <t>near_ir_albedo_for_diffuse_radiation', 'uv_visible_albedo_for_diffuse_radiation'</t>
+  </si>
+  <si>
+    <t>surface_solar_radiation_downwards</t>
+  </si>
+  <si>
+    <t>ssrd_acc</t>
+  </si>
+  <si>
+    <t>path to accumulated ERA 5 data (ssrd). Unit: J/m2</t>
+  </si>
+  <si>
+    <t>file_name_IEC_power_curves</t>
+  </si>
+  <si>
+    <t>Wind speed IEC Classes</t>
+  </si>
+  <si>
+    <t>Wind turbine power curves for three IEC classes</t>
+  </si>
+  <si>
+    <t>file_name_resource_raster</t>
+  </si>
+  <si>
+    <t>ECU_wind-speed_100m</t>
+  </si>
+  <si>
+    <t>Resource raster naming convention in MSR_Creator Outputs</t>
+  </si>
+  <si>
+    <t>file_name_regions</t>
+  </si>
+  <si>
+    <t>region_names</t>
+  </si>
+  <si>
+    <t>File name of csv file carrying list of regions for which MSR hourly profiles will be created.</t>
+  </si>
+  <si>
+    <t>file_name_region_utc_offset</t>
+  </si>
+  <si>
+    <t>region_utc_offsets</t>
+  </si>
+  <si>
+    <t>parameters</t>
+  </si>
+  <si>
+    <t>hours_in_year</t>
+  </si>
+  <si>
+    <t>reference_year</t>
+  </si>
+  <si>
+    <t>The reference year used for fitting linear regression in wind speed bias-correction</t>
+  </si>
+  <si>
+    <t>weather_years</t>
+  </si>
+  <si>
+    <t>List of weather years</t>
+  </si>
+  <si>
+    <t>elevation_threshold</t>
+  </si>
+  <si>
+    <t>wind_hub_height</t>
+  </si>
+  <si>
+    <t>Units: meters</t>
+  </si>
+  <si>
+    <t>configurations</t>
+  </si>
+  <si>
+    <t>run_code_for_solar_pv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Options=[0-No, 1-Yes]. </t>
+  </si>
+  <si>
+    <t>run_code_for_solar_csp</t>
+  </si>
+  <si>
+    <t>run_code_for_wind</t>
+  </si>
+  <si>
+    <t>run_code_for_offshore_wind</t>
+  </si>
+  <si>
+    <t>paths</t>
+  </si>
+  <si>
+    <t>input_folder_datasets</t>
+  </si>
+  <si>
+    <t>C:\Users\mastt\OneDrive - VITO\Documents\21_WP1\RawData\model_supply_regions\workflow\inputs\2022 MSR Toolset Inputs</t>
+  </si>
+  <si>
+    <t>Folder path where input datasets are located.</t>
+  </si>
+  <si>
+    <t>output_folder</t>
+  </si>
+  <si>
+    <t>C:\Dev\model_supply_regions\Model-Supply-Regions-MSR-Toolset\outputs</t>
+  </si>
+  <si>
+    <t>Folder path where outputs are located.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,37 +314,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor theme="0" tint="-0.14999847407452621"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -364,148 +338,113 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="15">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2" displayName="Table2" ref="A1:C3" totalsRowShown="0">
-  <autoFilter ref="A1:C3" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C12" displayName="Table4" name="Table4" id="1" totalsRowShown="0">
+  <autoFilter ref="A1:C12"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="paths"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="value"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="comments"/>
+    <tableColumn name="datasets" id="1"/>
+    <tableColumn name="value" id="2"/>
+    <tableColumn name="comments" id="3"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table1" displayName="Table1" ref="A1:C5" totalsRowShown="0">
-  <autoFilter ref="A1:C5" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C6" displayName="Table5" name="Table5" id="2" totalsRowShown="0">
+  <autoFilter ref="A1:C6"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="configurations"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="value"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="comments"/>
+    <tableColumn name="parameters" id="1"/>
+    <tableColumn name="value" id="2"/>
+    <tableColumn name="comments" id="3"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table5" displayName="Table5" ref="A1:C4" totalsRowShown="0">
-  <autoFilter ref="A1:C4" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C5" displayName="Table1" name="Table1" id="3" totalsRowShown="0">
+  <autoFilter ref="A1:C5"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="parameters"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="value"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="comments"/>
+    <tableColumn name="configurations" id="1"/>
+    <tableColumn name="value" id="2"/>
+    <tableColumn name="comments" id="3"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table4" displayName="Table4" ref="A1:C13" totalsRowShown="0">
-  <autoFilter ref="A1:C13" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C3" displayName="Table2" name="Table2" id="4" totalsRowShown="0">
+  <autoFilter ref="A1:C3"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="datasets"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="value"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="comments" dataDxfId="0"/>
+    <tableColumn name="paths" id="1"/>
+    <tableColumn name="value" id="2"/>
+    <tableColumn name="comments" id="3"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
@@ -514,10 +453,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -555,71 +494,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -647,7 +586,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -670,11 +609,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -683,13 +622,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -699,7 +638,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -708,7 +647,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -717,7 +656,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -725,10 +664,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -793,49 +732,49 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="4" width="36.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="58.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="52.86214285714286" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
+      <c r="A1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>48</v>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="46.5" customFormat="1" s="1">
+      <c r="A2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="33" customFormat="1" s="1">
+      <c r="A3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -847,71 +786,71 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.54296875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="14" width="48.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="9" width="20.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="60.71928571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+      <c r="A1" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="8">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="6">
         <v>0</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="12">
+      <c r="C2" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5" customFormat="1" s="1">
+      <c r="A3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="13">
         <v>0</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="12">
+      <c r="C3" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5" customFormat="1" s="1">
+      <c r="A4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="13">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="C4" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5" customFormat="1" s="1">
+      <c r="A5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="13">
         <v>0</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>39</v>
+      <c r="C5" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -923,54 +862,78 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="8" width="21.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="9" width="14.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="11.719285714285713" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="7" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+      <c r="A1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="8">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="6">
         <v>8784</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="9">
+      <c r="C2" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="7">
+        <v>2013</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="6">
+        <v>2013</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="6">
         <v>3000</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="8">
+      <c r="C5" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="6">
         <v>100</v>
       </c>
-      <c r="C4" t="s">
-        <v>36</v>
+      <c r="C6" s="5" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -982,159 +945,147 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="36.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.26953125" style="6" customWidth="1"/>
+    <col min="1" max="1" style="4" width="36.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="36.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="36.71928571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="33" customFormat="1" s="1">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="33" customFormat="1" s="1">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="33" customFormat="1" s="1">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="4" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5" customFormat="1" s="1">
+      <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="60" customFormat="1" s="1">
+      <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="4" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="46.5" customFormat="1" s="1">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="4" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="33" customFormat="1" s="1">
+      <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="4" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="33" customFormat="1" s="1">
+      <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="33" customFormat="1" s="1">
+      <c r="A10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C10" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="46.5" customFormat="1" s="1">
+      <c r="A11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>56</v>
-      </c>
+      <c r="C11" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5" customFormat="1" s="1">
+      <c r="A12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2_profile_generator/control_file_profile_generator.xlsx
+++ b/2_profile_generator/control_file_profile_generator.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vub-my.sharepoint.com/personal/sebastian_sterl_vub_be/Documents/Documenten/VUB Work Files/26001 MSR tutorial/2_profile_generator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vub-my.sharepoint.com/personal/sebastian_sterl_vub_be/Documents/Documenten/VUB Work Files/MSR code repo/2_profile_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="11_24EDF2EF255E430C8C5E746C6E0F651936CC1D52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBA49803-257B-4574-9CE8-DB9E1DDFDC98}"/>
+  <xr:revisionPtr revIDLastSave="171" documentId="11_24EDF2EF255E430C8C5E746C6E0F651936CC1D52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63D87035-3069-45B6-8D89-03563BA18ED8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="paths" sheetId="1" r:id="rId1"/>
@@ -85,9 +85,6 @@
     <t>wind_hub_height</t>
   </si>
   <si>
-    <t>Units: meters</t>
-  </si>
-  <si>
     <t>configurations</t>
   </si>
   <si>
@@ -269,9 +266,6 @@
     </r>
   </si>
   <si>
-    <t>The reference year used for fitting linear regression in wind speed bias-correction.</t>
-  </si>
-  <si>
     <t>t2m</t>
   </si>
   <si>
@@ -341,6 +335,52 @@
   </si>
   <si>
     <t>2012; 2013; 2014</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[only for wind]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Units: meters</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[only for wind]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The reference year used for fitting linear regression in wind speed bias-correction.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -947,7 +987,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -958,24 +998,24 @@
     </row>
     <row r="2" spans="1:3" s="1" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1011,24 +1051,24 @@
     </row>
     <row r="2" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
@@ -1036,10 +1076,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -1047,10 +1087,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -1058,10 +1098,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -1069,10 +1109,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -1080,10 +1120,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -1116,7 +1156,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -1147,7 +1187,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>1</v>
@@ -1158,46 +1198,46 @@
     </row>
     <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="14">
         <v>0</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="15">
         <v>0</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="15">
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="15">
         <v>0</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1237,10 +1277,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1251,7 +1291,7 @@
         <v>2012</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1262,7 +1302,7 @@
         <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
